--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desktop_files\PRISMA_gallery\PRISMA_assessment_git\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khtmo\OneDrive - UNSW\University\PhD_Chapters\prisma_evaluation\PRISMA_epidemiology\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADA7B4B-405C-41D7-B674-6792AD35DF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0774E9-B76C-4B02-8879-6BBC563F2290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="4" xr2:uid="{41511D95-B5DD-4FBB-860E-1C6E5A994D16}"/>
+    <workbookView xWindow="57480" yWindow="-12735" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{41511D95-B5DD-4FBB-860E-1C6E5A994D16}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -4535,20 +4535,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4923,11 +4923,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -5028,10 +5028,10 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
@@ -5039,8 +5039,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
       <c r="C14" t="s">
         <v>26</v>
       </c>
@@ -5144,11 +5144,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
@@ -5162,10 +5162,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="20" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
@@ -5173,8 +5173,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
       <c r="C27" t="s">
         <v>26</v>
       </c>
@@ -5191,10 +5191,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>49</v>
       </c>
       <c r="C29" t="s">
@@ -5202,17 +5202,17 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
       <c r="C30" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>51</v>
       </c>
       <c r="C31" t="s">
@@ -5220,17 +5220,17 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
       <c r="C32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C33" t="s">
@@ -5238,17 +5238,17 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
       <c r="C34" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>55</v>
       </c>
       <c r="C35" t="s">
@@ -5256,8 +5256,8 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
       <c r="C36" t="s">
         <v>26</v>
       </c>
@@ -5274,10 +5274,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C38" t="s">
@@ -5285,17 +5285,17 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
       <c r="C39" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="20" t="s">
         <v>61</v>
       </c>
       <c r="C40" t="s">
@@ -5303,8 +5303,8 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
       <c r="C41" t="s">
         <v>26</v>
       </c>
@@ -5321,10 +5321,10 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="20" t="s">
         <v>65</v>
       </c>
       <c r="C43" t="s">
@@ -5332,17 +5332,17 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="20"/>
       <c r="C44" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="20" t="s">
         <v>67</v>
       </c>
       <c r="C45" t="s">
@@ -5350,8 +5350,8 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
       <c r="C46" t="s">
         <v>26</v>
       </c>
@@ -5368,10 +5368,10 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="20" t="s">
         <v>71</v>
       </c>
       <c r="C48" t="s">
@@ -5379,17 +5379,17 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
+      <c r="A49" s="19"/>
+      <c r="B49" s="20"/>
       <c r="C49" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C50" t="s">
@@ -5397,17 +5397,17 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
+      <c r="A51" s="19"/>
+      <c r="B51" s="20"/>
       <c r="C51" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="20" t="s">
         <v>75</v>
       </c>
       <c r="C52" t="s">
@@ -5415,18 +5415,18 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19"/>
+      <c r="A53" s="19"/>
+      <c r="B53" s="20"/>
       <c r="C53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="20" t="s">
+      <c r="A54" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
     </row>
     <row r="55" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
@@ -5440,10 +5440,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="20" t="s">
         <v>78</v>
       </c>
       <c r="C56" t="s">
@@ -5451,17 +5451,17 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="20"/>
       <c r="C57" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C58" t="s">
@@ -5469,17 +5469,17 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="20"/>
       <c r="C59" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="20" t="s">
         <v>82</v>
       </c>
       <c r="C60" t="s">
@@ -5487,17 +5487,17 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="18"/>
-      <c r="B61" s="19"/>
+      <c r="A61" s="19"/>
+      <c r="B61" s="20"/>
       <c r="C61" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="20" t="s">
         <v>84</v>
       </c>
       <c r="C62" t="s">
@@ -5508,17 +5508,17 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="20"/>
       <c r="C63" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="20" t="s">
         <v>87</v>
       </c>
       <c r="C64" t="s">
@@ -5526,17 +5526,17 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="18"/>
-      <c r="B65" s="19"/>
+      <c r="A65" s="19"/>
+      <c r="B65" s="20"/>
       <c r="C65" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="20" t="s">
         <v>89</v>
       </c>
       <c r="C66" t="s">
@@ -5544,28 +5544,27 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="18"/>
-      <c r="B67" s="19"/>
+      <c r="A67" s="19"/>
+      <c r="B67" s="20"/>
       <c r="C67" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A62:A63"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="B38:B39"/>
@@ -5580,19 +5579,20 @@
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25920,20 +25920,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0f215fce-4250-43fe-b50b-13e349863264" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0f215fce-4250-43fe-b50b-13e349863264" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26184,19 +26184,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E7A45B-025E-400E-8F21-C9E980C500C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447008E2-54EE-4043-8FF7-C892031CCDC5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0f215fce-4250-43fe-b50b-13e349863264"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E7A45B-025E-400E-8F21-C9E980C500C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
